--- a/artfynd/A 56916-2019 artfynd.xlsx
+++ b/artfynd/A 56916-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 56916-2019 artfynd.xlsx
+++ b/artfynd/A 56916-2019 artfynd.xlsx
@@ -1153,7 +1153,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122369191</v>
+        <v>122369192</v>
       </c>
       <c r="B6" t="n">
         <v>56266</v>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1240,12 +1240,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2024-07-08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 56916-2019 artfynd.xlsx
+++ b/artfynd/A 56916-2019 artfynd.xlsx
@@ -1153,7 +1153,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122369192</v>
+        <v>122369191</v>
       </c>
       <c r="B6" t="n">
         <v>56266</v>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1240,12 +1240,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-07-08</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 56916-2019 artfynd.xlsx
+++ b/artfynd/A 56916-2019 artfynd.xlsx
@@ -1156,7 +1156,7 @@
         <v>122369191</v>
       </c>
       <c r="B6" t="n">
-        <v>56266</v>
+        <v>56271</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 56916-2019 artfynd.xlsx
+++ b/artfynd/A 56916-2019 artfynd.xlsx
@@ -1153,7 +1153,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122369191</v>
+        <v>122369192</v>
       </c>
       <c r="B6" t="n">
         <v>56271</v>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1240,12 +1240,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2024-07-08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 56916-2019 artfynd.xlsx
+++ b/artfynd/A 56916-2019 artfynd.xlsx
@@ -1153,7 +1153,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122369192</v>
+        <v>122369191</v>
       </c>
       <c r="B6" t="n">
         <v>56271</v>
@@ -1171,11 +1171,6 @@
       <c r="E6" t="n">
         <v>205998</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Nordfladdermus</t>
-        </is>
-      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>Eptesicus nilssonii</t>
@@ -1188,7 +1183,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1240,12 +1235,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-07-08</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 56916-2019 artfynd.xlsx
+++ b/artfynd/A 56916-2019 artfynd.xlsx
@@ -1156,7 +1156,7 @@
         <v>122369191</v>
       </c>
       <c r="B6" t="n">
-        <v>56271</v>
+        <v>56275</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1170,6 +1170,11 @@
       </c>
       <c r="E6" t="n">
         <v>205998</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>

--- a/artfynd/A 56916-2019 artfynd.xlsx
+++ b/artfynd/A 56916-2019 artfynd.xlsx
@@ -1153,7 +1153,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122369191</v>
+        <v>122369192</v>
       </c>
       <c r="B6" t="n">
         <v>56275</v>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1240,12 +1240,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2024-07-08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 56916-2019 artfynd.xlsx
+++ b/artfynd/A 56916-2019 artfynd.xlsx
@@ -1153,7 +1153,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122369192</v>
+        <v>122369191</v>
       </c>
       <c r="B6" t="n">
         <v>56275</v>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1240,12 +1240,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-07-08</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 56916-2019 artfynd.xlsx
+++ b/artfynd/A 56916-2019 artfynd.xlsx
@@ -1153,10 +1153,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122369191</v>
+        <v>122369192</v>
       </c>
       <c r="B6" t="n">
-        <v>56275</v>
+        <v>56276</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1240,12 +1240,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2024-07-08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AD6" t="b">
